--- a/etf_holdings/2026-09-07_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-07_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.64%480,000</t>
+          <t>8.14%480,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.64%</t>
+          <t>8.14%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>+0.60%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.63%364,000</t>
+          <t>7.70%364,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.63%</t>
+          <t>7.70%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.18%558,000</t>
+          <t>6.80%558,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.18%</t>
+          <t>6.80%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.57%310,000</t>
+          <t>6.25%310,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.57%</t>
+          <t>6.25%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.5%2070</t>
+          <t>+6.5%5490</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>+6.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2070</v>
+        <v>5490</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.14%665,000</t>
+          <t>5.34%273,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>5.34%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>665000</v>
+        <v>273000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.11%1,570,000</t>
+          <t>5.31%1,570,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.11%</t>
+          <t>5.31%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+6.5%5490</t>
+          <t>-3.5%2070</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+6.5%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5490</v>
+        <v>2070</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.07%273,000</t>
+          <t>4.91%665,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.07%</t>
+          <t>4.91%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>273000</v>
+        <v>665000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.25%1,127,000</t>
+          <t>4.50%1,127,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.14%212,000</t>
+          <t>4.15%212,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.01%529,000</t>
+          <t>3.96%529,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.42%54,300</t>
+          <t>3.72%54,300</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.96%245,000</t>
+          <t>3.03%245,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>3.03%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,25 +1236,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.47%1050</t>
+          <t>+9.78%6565</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>+9.78%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1050</v>
+        <v>6565</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.81%739,000</t>
+          <t>2.81%120,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1263,11 +1263,11 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>739000</v>
+        <v>120000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+9.78%6565</t>
+          <t>-0.47%1050</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+9.78%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6565</v>
+        <v>1050</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.59%120,000</t>
+          <t>2.77%739,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>120000</v>
+        <v>739000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:54</t>
+          <t>2026-09-07 19:29:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.46%750,000</t>
+          <t>2.57%750,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4991環宇-KY</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.6%494</t>
+          <t>+2.95%2265</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>+2.95%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>494</v>
+        <v>2265</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.15%1,200,000</t>
+          <t>2.19%271,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1200000</v>
+        <v>271000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>4991環宇-KY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+2.95%2265</t>
+          <t>-0.6%494</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+2.95%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2265</v>
+        <v>494</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.15%271,000</t>
+          <t>2.11%1,200,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>271000</v>
+        <v>1200000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.10%42,000</t>
+          <t>2.08%42,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.81%158,400</t>
+          <t>1.73%158,400</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7734印能科技</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.87%2915</t>
+          <t>+2.07%2460</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>+2.07%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2915</v>
+        <v>2460</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.56%150,000</t>
+          <t>1.57%179,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>150000</v>
+        <v>179000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,25 +1724,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>7734印能科技</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+2.07%2460</t>
+          <t>+0.87%2915</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+2.07%</t>
+          <t>+0.87%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2460</v>
+        <v>2915</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.56%179,000</t>
+          <t>1.56%150,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1751,11 +1751,11 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>179000</v>
+        <v>150000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.51%306,000</t>
+          <t>1.49%306,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,25 +1846,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3131弘塑</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.92%2490</t>
+          <t>+7.13%2555</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.92%</t>
+          <t>+7.13%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2490</v>
+        <v>2555</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.38%149,139</t>
+          <t>1.38%152,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1873,11 +1873,11 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>149139</v>
+        <v>152000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,25 +1968,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-4.62%1240</t>
+          <t>-2.92%2490</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-4.62%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1240</v>
+        <v>2490</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.32%282,000</t>
+          <t>1.32%149,139</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1995,11 +1995,11 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>282000</v>
+        <v>149139</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3131弘塑</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+7.13%2555</t>
+          <t>-4.62%1240</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+7.13%</t>
+          <t>-4.62%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2555</v>
+        <v>1240</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.31%152,000</t>
+          <t>1.25%282,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>152000</v>
+        <v>282000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.01%1,400,000</t>
+          <t>0.97%1,400,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.93%198,000</t>
+          <t>0.97%198,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:55</t>
+          <t>2026-09-07 19:29:34</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8210勤誠</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-4.97%937</t>
+          <t>-1.06%7000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-4.97%</t>
+          <t>-1.06%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>937</v>
+        <v>7000</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.60%168,000</t>
+          <t>0.57%23,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>168000</v>
+        <v>23000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>8210勤誠</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.06%7000</t>
+          <t>-4.97%937</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-4.97%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>7000</v>
+        <v>937</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.59%23,000</t>
+          <t>0.56%168,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>23000</v>
+        <v>168000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.55%250,000</t>
+          <t>0.51%250,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.39%110,000</t>
+          <t>0.38%110,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.35%400,000</t>
+          <t>0.34%400,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.33%146,000</t>
+          <t>0.34%146,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.11%211,000</t>
+          <t>0.12%211,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,25 +2883,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3163波若威</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.97%752</t>
+          <t>+10%143</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.97%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>752</v>
+        <v>143</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.04%13,300</t>
+          <t>0.04%78,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>13300</v>
+        <v>78000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3163波若威</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+10%143</t>
+          <t>-2.97%752</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>143</v>
+        <v>752</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.04%78,000</t>
+          <t>0.04%13,300</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,11 +2971,11 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>78000</v>
+        <v>13300</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-4.27%4040</t>
+          <t>+10%462</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-4.27%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>4040</v>
+        <v>462</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.02%1,000</t>
+          <t>0.02%10,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+10%462</t>
+          <t>-4.27%4040</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-4.27%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>462</v>
+        <v>4040</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.02%10,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:56</t>
+          <t>2026-09-07 19:29:35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:58</t>
+          <t>2026-09-07 19:29:36</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:58</t>
+          <t>2026-09-07 19:29:36</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:58</t>
+          <t>2026-09-07 19:29:36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:58</t>
+          <t>2026-09-07 19:29:36</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-07 18:47:58</t>
+          <t>2026-09-07 19:29:36</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-07_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-07_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:32</t>
+          <t>2026-09-07 19:59:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:34</t>
+          <t>2026-09-07 19:59:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:35</t>
+          <t>2026-09-07 19:59:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:36</t>
+          <t>2026-09-07 19:59:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:36</t>
+          <t>2026-09-07 19:59:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:36</t>
+          <t>2026-09-07 19:59:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:36</t>
+          <t>2026-09-07 19:59:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-07 19:29:36</t>
+          <t>2026-09-07 19:59:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-07_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-07_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:46</t>
+          <t>2026-09-07 22:26:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:48</t>
+          <t>2026-09-07 22:26:23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:49</t>
+          <t>2026-09-07 22:26:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:50</t>
+          <t>2026-09-07 22:26:26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:50</t>
+          <t>2026-09-07 22:26:26</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:50</t>
+          <t>2026-09-07 22:26:26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:50</t>
+          <t>2026-09-07 22:26:26</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-07 19:59:50</t>
+          <t>2026-09-07 22:26:26</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-07_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-07_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:22</t>
+          <t>2026-09-07 23:03:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:23</t>
+          <t>2026-09-07 23:03:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:24</t>
+          <t>2026-09-07 23:03:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:26</t>
+          <t>2026-09-07 23:03:54</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:26</t>
+          <t>2026-09-07 23:03:54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:26</t>
+          <t>2026-09-07 23:03:54</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:26</t>
+          <t>2026-09-07 23:03:54</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-07 22:26:26</t>
+          <t>2026-09-07 23:03:54</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
